--- a/Result/profitability/6127.xlsx
+++ b/Result/profitability/6127.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03</v>
+        <v>-0.10625</v>
       </c>
       <c r="N2" t="n">
-        <v>15.0575</v>
+        <v>13.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.035</v>
+        <v>-0.09374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.11875</v>
+        <v>13.3475</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>-0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03624999999999999</v>
+        <v>-0.1625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.89875</v>
+        <v>13.01375</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0575</v>
+        <v>-0.10375</v>
       </c>
       <c r="N5" t="n">
-        <v>15.76625</v>
+        <v>15.01125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.83</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.13375</v>
+        <v>-0.295</v>
       </c>
       <c r="N6" t="n">
-        <v>8.887499999999999</v>
+        <v>7.72125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2524999999999999</v>
+        <v>-0.27125</v>
       </c>
       <c r="N7" t="n">
-        <v>9.234999999999999</v>
+        <v>8.772499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.19375</v>
+        <v>-0.20375</v>
       </c>
       <c r="N8" t="n">
-        <v>10.37625</v>
+        <v>10.1525</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9348,15 +9348,15 @@
         <v>10.24</v>
       </c>
       <c r="G71" t="n">
-        <v>-58</v>
+        <v>-51</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-21.37%</t>
+          <t>-18.87%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
         <v>-20</v>
@@ -9475,15 +9475,15 @@
         <v>13.53</v>
       </c>
       <c r="G72" t="n">
-        <v>-31</v>
+        <v>-38</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-13.93%</t>
+          <t>-16.97%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="J72" t="n">
         <v>74</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>267</v>
+      </c>
+      <c r="D75" t="n">
+        <v>256</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-65</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-24.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-64</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.40125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1568627450980391</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2988313856427379</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.58984375</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
